--- a/results/monthly_investor_report_2026-10-28.xlsx
+++ b/results/monthly_investor_report_2026-10-28.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2150769131151307</v>
+        <v>0.2150769987984023</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21507.69131151307</v>
+        <v>21507.69987984023</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.05844149786751873</v>
+        <v>0.05844167403239653</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1256.941695917042</v>
+        <v>1256.945985564237</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>375.7467317429691</v>
+        <v>375.7467942815007</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>336.0711478281098</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.096037496334751</v>
+        <v>1.09604080020817</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1960104173232019</v>
+        <v>0.1960103712894062</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19601.04173232019</v>
+        <v>19601.03712894061</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.03311743610603668</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>649.1362471818724</v>
+        <v>649.1360947297434</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>130.8959760018107</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>120.0852874054473</v>
+        <v>120.0852816272273</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6343406352798925</v>
+        <v>0.6343400811578253</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1889126695616674</v>
+        <v>0.1889126299121916</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18891.26695616674</v>
+        <v>18891.26299121916</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.02241116988474068</v>
+        <v>0.02241116791989972</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>423.3753930926406</v>
+        <v>423.3752671151997</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>85.11572989290467</v>
+        <v>85.11572972933165</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>76.81473124867266</v>
+        <v>76.81472520436542</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2899226069649136</v>
+        <v>0.2899223092380265</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000.00000000001</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1370,22 +1370,22 @@
         <v>364.75</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.01299453751914625</v>
+        <v>-0.01299463649111321</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.02199403077497974</v>
+        <v>0.02199409951792641</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.08916911887571016</v>
+        <v>0.08916908802962803</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>360.0102424398914</v>
+        <v>360.0102063398664</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>372.7723227251739</v>
+        <v>372.7723477991636</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>397.2744361099153</v>
+        <v>397.2744248588069</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>346.5125</v>
@@ -1427,25 +1427,25 @@
         <v>83.25</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.0773005255414696</v>
+        <v>-0.07730059814576073</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.02241116988474068</v>
+        <v>0.02241116791989972</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.1086499313597238</v>
+        <v>0.1086497453521593</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>76.81473124867266</v>
+        <v>76.81472520436542</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>85.11572989290467</v>
+        <v>85.11572972933165</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>92.295106785697</v>
+        <v>92.29509130056726</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>76.81473124867266</v>
+        <v>76.81472520436542</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>0.01757102788880816</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.0942064905399887</v>
+        <v>0.09420646554764889</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>197.2035465208114</v>
@@ -1499,7 +1499,7 @@
         <v>203.3106944775642</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>218.6224601491429</v>
+        <v>218.6224551556734</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>189.8100028991699</v>
@@ -1541,22 +1541,22 @@
         <v>355</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.03252680765408428</v>
+        <v>-0.03252668807429737</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.05844149786751873</v>
+        <v>0.05844167403239653</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1756285683893573</v>
+        <v>0.1756284535162542</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>343.4529832828001</v>
+        <v>343.4530257336244</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>375.7467317429691</v>
+        <v>375.7467942815007</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>417.3481417782218</v>
+        <v>417.3481009982702</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>336.0711478281098</v>
@@ -1598,7 +1598,7 @@
         <v>126.6999969482422</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.05220765352896592</v>
+        <v>-0.05220769913449161</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>0.03311743610603668</v>
@@ -1607,7 +1607,7 @@
         <v>0.05777779972896546</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>120.0852874054473</v>
+        <v>120.0852816272273</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>130.8959760018107</v>
@@ -1616,7 +1616,7 @@
         <v>134.0204439975783</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>120.0852874054473</v>
+        <v>120.0852816272273</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1769,25 +1769,25 @@
         <v>63</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.06619350494083276</v>
+        <v>-0.06619358886274462</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.02538799556850624</v>
+        <v>-0.02538782488734992</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.07228325784374789</v>
+        <v>0.07228317000253504</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>58.82980918872754</v>
+        <v>58.82980390164709</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>61.40055627918411</v>
+        <v>61.40056703209696</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>67.55384524415611</v>
+        <v>67.55383971015971</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>58.82980918872754</v>
+        <v>58.82980390164709</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>-0.01693890855618208</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.1049996640028169</v>
+        <v>0.1049996301466382</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>64.68715460855189</v>
@@ -1841,7 +1841,7 @@
         <v>69.79733749251108</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>78.4549761442</v>
+        <v>78.45497374041132</v>
       </c>
       <c r="K16" s="21" t="n">
         <v>64.68715460855189</v>
@@ -1883,7 +1883,7 @@
         <v>230</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.1062914431538463</v>
+        <v>-0.1062914365179825</v>
       </c>
       <c r="F17" s="22" t="n">
         <v>-0.03410138248847927</v>
@@ -1892,7 +1892,7 @@
         <v>0.07484769327601914</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>205.5529680746153</v>
+        <v>205.552969600864</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>222.1566820276498</v>
@@ -1901,7 +1901,7 @@
         <v>247.2149694534844</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>205.5529680746153</v>
+        <v>205.552969600864</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.02053819830186686</v>
+        <v>0.02053819830186682</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.02199403077497974</v>
+        <v>0.02199409951792641</v>
       </c>
     </row>
     <row r="5">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.02157502358556948</v>
+        <v>0.02157502358556944</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.02241116988474068</v>
+        <v>0.02241116791989972</v>
       </c>
     </row>
     <row r="6">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.02157901039614461</v>
+        <v>0.02157901039614466</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.01757102788880816</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.02666035517167634</v>
+        <v>0.02666035517167641</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>0.05844149786751873</v>
+        <v>0.05844167403239653</v>
       </c>
     </row>
     <row r="8">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.02257989782760708</v>
+        <v>0.02257989782760712</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>0.03311743610603668</v>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.01919087639488939</v>
+        <v>0.01919087639488928</v>
       </c>
       <c r="K10" s="24" t="n">
         <v>0.04170591714306782</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.0197687922477363</v>
+        <v>0.01976879224773625</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.003406581210156023</v>
+        <v>0.003406771384319551</v>
       </c>
     </row>
     <row r="12">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.02583200132392652</v>
+        <v>0.02583200132392654</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.001239185781908958</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.02382245399754359</v>
+        <v>0.02382245399754362</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>-0.02538799556850624</v>
+        <v>-0.02538782488734992</v>
       </c>
     </row>
     <row r="15">
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J15" s="28" t="n">
-        <v>0.03254720262450492</v>
+        <v>0.03254720262450491</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0.04060870280653839</v>
+        <v>0.04060881671957561</v>
       </c>
     </row>
     <row r="16">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="J17" s="26" t="n">
-        <v>0.02513467276230041</v>
+        <v>0.02513467276230038</v>
       </c>
       <c r="K17" s="26" t="n">
         <v>-0.03410138248847927</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="J18" s="28" t="n">
-        <v>0.02719901791902606</v>
+        <v>0.02719901791902594</v>
       </c>
       <c r="K18" s="28" t="n">
         <v>0.03223836752309794</v>
@@ -2726,7 +2726,7 @@
         <v>0.03497853363382911</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>0.08095244598942708</v>
+        <v>0.08095237804027433</v>
       </c>
     </row>
     <row r="20">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J20" s="28" t="n">
-        <v>0.02721823312977668</v>
+        <v>0.02721823312977672</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>0.05690249294878802</v>
+        <v>0.05690245897421164</v>
       </c>
     </row>
   </sheetData>
@@ -2802,7 +2802,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2921,7 +2921,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3172,7 +3172,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11165.400390625</v>
+        <v>10759.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13605.29202148437</v>
+        <v>13597.81602050781</v>
       </c>
     </row>
     <row r="6">
@@ -3297,7 +3297,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
